--- a/grepxcel/examples/01_simple_invoice/pattern.xlsx
+++ b/grepxcel/examples/01_simple_invoice/pattern.xlsx
@@ -682,7 +682,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>AB123456</t>
+          <t>AB\d+</t>
         </is>
       </c>
     </row>
@@ -762,7 +762,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>.*</t>
+          <t>.*@.*</t>
         </is>
       </c>
     </row>
@@ -782,7 +782,11 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="D16" s="3" t="n"/>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>\d+</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -800,7 +804,11 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="D17" s="3" t="n"/>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>\d+</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -818,7 +826,11 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="D18" s="3" t="n"/>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>\d+</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
